--- a/docs/package/05_Delivery/Upload_Templates/Remittance_Schedule_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Remittance_Schedule_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="85">
   <si>
     <t xml:space="preserve">Code</t>
   </si>
@@ -39,6 +39,27 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All active insurers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group remittances by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proof of payment required</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
@@ -81,21 +102,21 @@
     <t xml:space="preserve">Other accepted headers</t>
   </si>
   <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code</t>
-  </si>
-  <si>
     <t xml:space="preserve">name</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
     <t xml:space="preserve">Values separated by commas (semicolons when a value has a comma)</t>
   </si>
   <si>
@@ -129,6 +150,42 @@
     <t xml:space="preserve">type</t>
   </si>
   <si>
+    <t xml:space="preserve">Remittance run, Billing run, Hold check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes or No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allInsurers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Monday to Friday, Cut-off days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paymentWindow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurer, Insurer and product line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">groupBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">runTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incepted up to the cut-off, Fully paid in the window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eligibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proofRequired</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active when empty</t>
   </si>
   <si>
@@ -156,12 +213,6 @@
     <t xml:space="preserve">Accounts &gt; Remittance &gt; Scheduling (no Upload button on this screen yet: a System Administrator uploads the file through the API route)</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/remittance-schedule/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -177,7 +228,7 @@
     <t xml:space="preserve">Required columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Code, Name, Frequency (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
+    <t xml:space="preserve">Name, Frequency (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
   </si>
   <si>
     <t xml:space="preserve">Header row</t>
@@ -213,10 +264,10 @@
     <t xml:space="preserve">Insurers take the insurer names separated by semicolons (names contain commas). With no insurer named, the schedule runs the automated remittances listed in Linked Processes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -224,9 +275,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -253,8 +304,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,6 +367,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -313,9 +416,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -336,6 +439,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -345,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -357,10 +467,17 @@
     <col min="7" max="7" width="42" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="31" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:16" ht="20" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -387,28 +504,49 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -418,7 +556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -431,22 +569,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -454,16 +592,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -471,16 +609,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +626,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -505,16 +643,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -522,19 +660,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -542,16 +680,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -559,13 +697,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -573,16 +711,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -590,16 +728,126 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -609,7 +857,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -618,111 +866,103 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>63</v>
-      </c>
       <c r="B12" s="4" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>83</v>
+      </c>
       <c r="B13" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
